--- a/r5-ELGA-MOPED-main/StructureDefinition-MopedUpdateBundleKA.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MopedUpdateBundleKA.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-29T09:14:27+00:00</t>
+    <t>2026-05-05T07:22:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MopedUpdateBundleKA.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MopedUpdateBundleKA.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-05T07:22:12+00:00</t>
+    <t>2026-05-15T07:39:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MopedUpdateBundleKA.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MopedUpdateBundleKA.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-15T07:39:15+00:00</t>
+    <t>2026-05-15T09:26:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -993,7 +993,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Patient {https://elga.moped.at/StructureDefinition/MopedPatient}
+    <t xml:space="preserve">Patient {https://elga.moped.at/StructureDefinition/MopedBasisPatientvbPK|https://elga.moped.at/StructureDefinition/MopedBasisPatientKlarname}
 </t>
   </si>
   <si>
@@ -2517,7 +2517,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="112.83984375" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="116.8828125" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MopedUpdateBundleKA.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MopedUpdateBundleKA.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13757" uniqueCount="708">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13758" uniqueCount="712">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-15T09:26:31+00:00</t>
+    <t>2026-05-22T08:08:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1326,8 +1326,21 @@
     <t>Bundle.entry:Entbindung.resource</t>
   </si>
   <si>
-    <t xml:space="preserve">Observation
+    <t>Vital Signs
+MeasurementResultsTests</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Observation {https://elga.moped.at/StructureDefinition/MopedObservationGeburtenanzahl|https://elga.moped.at/StructureDefinition/MopedObservationEntbindungsart}
 </t>
+  </si>
+  <si>
+    <t>Measurements and simple assertions</t>
+  </si>
+  <si>
+    <t>Measurements and simple assertions made about a patient, device or other subject.</t>
+  </si>
+  <si>
+    <t>Used for simple observations such as device measurements, laboratory atomic results, vital signs, height, weight, smoking status, comments, etc.  Other resources are used to provide context for observations such as laboratory reports, etc.</t>
   </si>
   <si>
     <t>Bundle.entry:Entbindung.search</t>
@@ -2517,7 +2530,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="116.8828125" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="133.94921875" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -20981,7 +20994,7 @@
       </c>
       <c r="C183" s="2"/>
       <c r="D183" t="s" s="2">
-        <v>20</v>
+        <v>419</v>
       </c>
       <c r="E183" s="2"/>
       <c r="F183" t="s" s="2">
@@ -20997,18 +21010,20 @@
         <v>20</v>
       </c>
       <c r="J183" t="s" s="2">
-        <v>81</v>
+        <v>20</v>
       </c>
       <c r="K183" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="L183" t="s" s="2">
-        <v>186</v>
+        <v>421</v>
       </c>
       <c r="M183" t="s" s="2">
-        <v>187</v>
-      </c>
-      <c r="N183" s="2"/>
+        <v>422</v>
+      </c>
+      <c r="N183" t="s" s="2">
+        <v>423</v>
+      </c>
       <c r="O183" s="2"/>
       <c r="P183" t="s" s="2">
         <v>20</v>
@@ -21066,7 +21081,7 @@
         <v>80</v>
       </c>
       <c r="AI183" t="s" s="2">
-        <v>188</v>
+        <v>20</v>
       </c>
       <c r="AJ183" t="s" s="2">
         <v>20</v>
@@ -21074,7 +21089,7 @@
     </row>
     <row r="184">
       <c r="A184" t="s" s="2">
-        <v>420</v>
+        <v>424</v>
       </c>
       <c r="B184" t="s" s="2">
         <v>189</v>
@@ -21174,7 +21189,7 @@
     </row>
     <row r="185">
       <c r="A185" t="s" s="2">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="B185" t="s" s="2">
         <v>193</v>
@@ -21274,7 +21289,7 @@
     </row>
     <row r="186">
       <c r="A186" t="s" s="2">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="B186" t="s" s="2">
         <v>194</v>
@@ -21376,7 +21391,7 @@
     </row>
     <row r="187">
       <c r="A187" t="s" s="2">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="B187" t="s" s="2">
         <v>195</v>
@@ -21480,7 +21495,7 @@
     </row>
     <row r="188">
       <c r="A188" t="s" s="2">
-        <v>424</v>
+        <v>428</v>
       </c>
       <c r="B188" t="s" s="2">
         <v>196</v>
@@ -21582,7 +21597,7 @@
     </row>
     <row r="189">
       <c r="A189" t="s" s="2">
-        <v>425</v>
+        <v>429</v>
       </c>
       <c r="B189" t="s" s="2">
         <v>202</v>
@@ -21684,7 +21699,7 @@
     </row>
     <row r="190">
       <c r="A190" t="s" s="2">
-        <v>426</v>
+        <v>430</v>
       </c>
       <c r="B190" t="s" s="2">
         <v>207</v>
@@ -21784,7 +21799,7 @@
     </row>
     <row r="191">
       <c r="A191" t="s" s="2">
-        <v>427</v>
+        <v>431</v>
       </c>
       <c r="B191" t="s" s="2">
         <v>211</v>
@@ -21884,7 +21899,7 @@
     </row>
     <row r="192">
       <c r="A192" t="s" s="2">
-        <v>428</v>
+        <v>432</v>
       </c>
       <c r="B192" t="s" s="2">
         <v>212</v>
@@ -21986,7 +22001,7 @@
     </row>
     <row r="193">
       <c r="A193" t="s" s="2">
-        <v>429</v>
+        <v>433</v>
       </c>
       <c r="B193" t="s" s="2">
         <v>213</v>
@@ -22090,7 +22105,7 @@
     </row>
     <row r="194">
       <c r="A194" t="s" s="2">
-        <v>430</v>
+        <v>434</v>
       </c>
       <c r="B194" t="s" s="2">
         <v>214</v>
@@ -22188,7 +22203,7 @@
     </row>
     <row r="195">
       <c r="A195" t="s" s="2">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="B195" t="s" s="2">
         <v>220</v>
@@ -22290,7 +22305,7 @@
     </row>
     <row r="196">
       <c r="A196" t="s" s="2">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c r="B196" t="s" s="2">
         <v>224</v>
@@ -22390,7 +22405,7 @@
     </row>
     <row r="197">
       <c r="A197" t="s" s="2">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="B197" t="s" s="2">
         <v>227</v>
@@ -22490,7 +22505,7 @@
     </row>
     <row r="198">
       <c r="A198" t="s" s="2">
-        <v>434</v>
+        <v>438</v>
       </c>
       <c r="B198" t="s" s="2">
         <v>230</v>
@@ -22590,7 +22605,7 @@
     </row>
     <row r="199">
       <c r="A199" t="s" s="2">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="B199" t="s" s="2">
         <v>233</v>
@@ -22690,7 +22705,7 @@
     </row>
     <row r="200">
       <c r="A200" t="s" s="2">
-        <v>436</v>
+        <v>440</v>
       </c>
       <c r="B200" t="s" s="2">
         <v>236</v>
@@ -22790,7 +22805,7 @@
     </row>
     <row r="201">
       <c r="A201" t="s" s="2">
-        <v>437</v>
+        <v>441</v>
       </c>
       <c r="B201" t="s" s="2">
         <v>240</v>
@@ -22890,7 +22905,7 @@
     </row>
     <row r="202">
       <c r="A202" t="s" s="2">
-        <v>438</v>
+        <v>442</v>
       </c>
       <c r="B202" t="s" s="2">
         <v>241</v>
@@ -22992,7 +23007,7 @@
     </row>
     <row r="203">
       <c r="A203" t="s" s="2">
-        <v>439</v>
+        <v>443</v>
       </c>
       <c r="B203" t="s" s="2">
         <v>242</v>
@@ -23096,7 +23111,7 @@
     </row>
     <row r="204">
       <c r="A204" t="s" s="2">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="B204" t="s" s="2">
         <v>243</v>
@@ -23196,7 +23211,7 @@
     </row>
     <row r="205">
       <c r="A205" t="s" s="2">
-        <v>441</v>
+        <v>445</v>
       </c>
       <c r="B205" t="s" s="2">
         <v>246</v>
@@ -23296,7 +23311,7 @@
     </row>
     <row r="206">
       <c r="A206" t="s" s="2">
-        <v>442</v>
+        <v>446</v>
       </c>
       <c r="B206" t="s" s="2">
         <v>249</v>
@@ -23398,7 +23413,7 @@
     </row>
     <row r="207">
       <c r="A207" t="s" s="2">
-        <v>443</v>
+        <v>447</v>
       </c>
       <c r="B207" t="s" s="2">
         <v>253</v>
@@ -23500,7 +23515,7 @@
     </row>
     <row r="208">
       <c r="A208" t="s" s="2">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="B208" t="s" s="2">
         <v>257</v>
@@ -23602,13 +23617,13 @@
     </row>
     <row r="209">
       <c r="A209" t="s" s="2">
-        <v>445</v>
+        <v>449</v>
       </c>
       <c r="B209" t="s" s="2">
         <v>167</v>
       </c>
       <c r="C209" t="s" s="2">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="D209" t="s" s="2">
         <v>20</v>
@@ -23704,7 +23719,7 @@
     </row>
     <row r="210">
       <c r="A210" t="s" s="2">
-        <v>447</v>
+        <v>451</v>
       </c>
       <c r="B210" t="s" s="2">
         <v>173</v>
@@ -23804,7 +23819,7 @@
     </row>
     <row r="211">
       <c r="A211" t="s" s="2">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="B211" t="s" s="2">
         <v>174</v>
@@ -23906,7 +23921,7 @@
     </row>
     <row r="212">
       <c r="A212" t="s" s="2">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="B212" t="s" s="2">
         <v>175</v>
@@ -24010,7 +24025,7 @@
     </row>
     <row r="213">
       <c r="A213" t="s" s="2">
-        <v>450</v>
+        <v>454</v>
       </c>
       <c r="B213" t="s" s="2">
         <v>176</v>
@@ -24036,7 +24051,7 @@
         <v>81</v>
       </c>
       <c r="K213" t="s" s="2">
-        <v>75</v>
+        <v>20</v>
       </c>
       <c r="L213" t="s" s="2">
         <v>177</v>
@@ -24110,7 +24125,7 @@
     </row>
     <row r="214">
       <c r="A214" t="s" s="2">
-        <v>451</v>
+        <v>455</v>
       </c>
       <c r="B214" t="s" s="2">
         <v>179</v>
@@ -24212,7 +24227,7 @@
     </row>
     <row r="215">
       <c r="A215" t="s" s="2">
-        <v>452</v>
+        <v>456</v>
       </c>
       <c r="B215" t="s" s="2">
         <v>184</v>
@@ -24238,7 +24253,7 @@
         <v>20</v>
       </c>
       <c r="K215" t="s" s="2">
-        <v>453</v>
+        <v>457</v>
       </c>
       <c r="L215" t="s" s="2">
         <v>271</v>
@@ -24312,7 +24327,7 @@
     </row>
     <row r="216">
       <c r="A216" t="s" s="2">
-        <v>454</v>
+        <v>458</v>
       </c>
       <c r="B216" t="s" s="2">
         <v>189</v>
@@ -24412,7 +24427,7 @@
     </row>
     <row r="217">
       <c r="A217" t="s" s="2">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="B217" t="s" s="2">
         <v>193</v>
@@ -24512,7 +24527,7 @@
     </row>
     <row r="218">
       <c r="A218" t="s" s="2">
-        <v>456</v>
+        <v>460</v>
       </c>
       <c r="B218" t="s" s="2">
         <v>194</v>
@@ -24614,7 +24629,7 @@
     </row>
     <row r="219">
       <c r="A219" t="s" s="2">
-        <v>457</v>
+        <v>461</v>
       </c>
       <c r="B219" t="s" s="2">
         <v>195</v>
@@ -24718,7 +24733,7 @@
     </row>
     <row r="220">
       <c r="A220" t="s" s="2">
-        <v>458</v>
+        <v>462</v>
       </c>
       <c r="B220" t="s" s="2">
         <v>196</v>
@@ -24820,7 +24835,7 @@
     </row>
     <row r="221">
       <c r="A221" t="s" s="2">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="B221" t="s" s="2">
         <v>202</v>
@@ -24922,7 +24937,7 @@
     </row>
     <row r="222">
       <c r="A222" t="s" s="2">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="B222" t="s" s="2">
         <v>207</v>
@@ -25022,7 +25037,7 @@
     </row>
     <row r="223">
       <c r="A223" t="s" s="2">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="B223" t="s" s="2">
         <v>211</v>
@@ -25122,7 +25137,7 @@
     </row>
     <row r="224">
       <c r="A224" t="s" s="2">
-        <v>462</v>
+        <v>466</v>
       </c>
       <c r="B224" t="s" s="2">
         <v>212</v>
@@ -25224,7 +25239,7 @@
     </row>
     <row r="225">
       <c r="A225" t="s" s="2">
-        <v>463</v>
+        <v>467</v>
       </c>
       <c r="B225" t="s" s="2">
         <v>213</v>
@@ -25328,7 +25343,7 @@
     </row>
     <row r="226">
       <c r="A226" t="s" s="2">
-        <v>464</v>
+        <v>468</v>
       </c>
       <c r="B226" t="s" s="2">
         <v>214</v>
@@ -25426,7 +25441,7 @@
     </row>
     <row r="227">
       <c r="A227" t="s" s="2">
-        <v>465</v>
+        <v>469</v>
       </c>
       <c r="B227" t="s" s="2">
         <v>220</v>
@@ -25528,7 +25543,7 @@
     </row>
     <row r="228">
       <c r="A228" t="s" s="2">
-        <v>466</v>
+        <v>470</v>
       </c>
       <c r="B228" t="s" s="2">
         <v>224</v>
@@ -25628,7 +25643,7 @@
     </row>
     <row r="229">
       <c r="A229" t="s" s="2">
-        <v>467</v>
+        <v>471</v>
       </c>
       <c r="B229" t="s" s="2">
         <v>227</v>
@@ -25728,7 +25743,7 @@
     </row>
     <row r="230">
       <c r="A230" t="s" s="2">
-        <v>468</v>
+        <v>472</v>
       </c>
       <c r="B230" t="s" s="2">
         <v>230</v>
@@ -25828,7 +25843,7 @@
     </row>
     <row r="231">
       <c r="A231" t="s" s="2">
-        <v>469</v>
+        <v>473</v>
       </c>
       <c r="B231" t="s" s="2">
         <v>233</v>
@@ -25928,7 +25943,7 @@
     </row>
     <row r="232">
       <c r="A232" t="s" s="2">
-        <v>470</v>
+        <v>474</v>
       </c>
       <c r="B232" t="s" s="2">
         <v>236</v>
@@ -26028,7 +26043,7 @@
     </row>
     <row r="233">
       <c r="A233" t="s" s="2">
-        <v>471</v>
+        <v>475</v>
       </c>
       <c r="B233" t="s" s="2">
         <v>240</v>
@@ -26128,7 +26143,7 @@
     </row>
     <row r="234">
       <c r="A234" t="s" s="2">
-        <v>472</v>
+        <v>476</v>
       </c>
       <c r="B234" t="s" s="2">
         <v>241</v>
@@ -26230,7 +26245,7 @@
     </row>
     <row r="235">
       <c r="A235" t="s" s="2">
-        <v>473</v>
+        <v>477</v>
       </c>
       <c r="B235" t="s" s="2">
         <v>242</v>
@@ -26334,7 +26349,7 @@
     </row>
     <row r="236">
       <c r="A236" t="s" s="2">
-        <v>474</v>
+        <v>478</v>
       </c>
       <c r="B236" t="s" s="2">
         <v>243</v>
@@ -26434,7 +26449,7 @@
     </row>
     <row r="237">
       <c r="A237" t="s" s="2">
-        <v>475</v>
+        <v>479</v>
       </c>
       <c r="B237" t="s" s="2">
         <v>246</v>
@@ -26534,7 +26549,7 @@
     </row>
     <row r="238">
       <c r="A238" t="s" s="2">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="B238" t="s" s="2">
         <v>249</v>
@@ -26636,7 +26651,7 @@
     </row>
     <row r="239">
       <c r="A239" t="s" s="2">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="B239" t="s" s="2">
         <v>253</v>
@@ -26738,7 +26753,7 @@
     </row>
     <row r="240">
       <c r="A240" t="s" s="2">
-        <v>478</v>
+        <v>482</v>
       </c>
       <c r="B240" t="s" s="2">
         <v>257</v>
@@ -26840,13 +26855,13 @@
     </row>
     <row r="241">
       <c r="A241" t="s" s="2">
-        <v>479</v>
+        <v>483</v>
       </c>
       <c r="B241" t="s" s="2">
         <v>167</v>
       </c>
       <c r="C241" t="s" s="2">
-        <v>480</v>
+        <v>484</v>
       </c>
       <c r="D241" t="s" s="2">
         <v>20</v>
@@ -26942,7 +26957,7 @@
     </row>
     <row r="242">
       <c r="A242" t="s" s="2">
-        <v>481</v>
+        <v>485</v>
       </c>
       <c r="B242" t="s" s="2">
         <v>173</v>
@@ -27042,7 +27057,7 @@
     </row>
     <row r="243">
       <c r="A243" t="s" s="2">
-        <v>482</v>
+        <v>486</v>
       </c>
       <c r="B243" t="s" s="2">
         <v>174</v>
@@ -27144,7 +27159,7 @@
     </row>
     <row r="244">
       <c r="A244" t="s" s="2">
-        <v>483</v>
+        <v>487</v>
       </c>
       <c r="B244" t="s" s="2">
         <v>175</v>
@@ -27248,7 +27263,7 @@
     </row>
     <row r="245">
       <c r="A245" t="s" s="2">
-        <v>484</v>
+        <v>488</v>
       </c>
       <c r="B245" t="s" s="2">
         <v>176</v>
@@ -27274,7 +27289,7 @@
         <v>81</v>
       </c>
       <c r="K245" t="s" s="2">
-        <v>75</v>
+        <v>20</v>
       </c>
       <c r="L245" t="s" s="2">
         <v>177</v>
@@ -27348,7 +27363,7 @@
     </row>
     <row r="246">
       <c r="A246" t="s" s="2">
-        <v>485</v>
+        <v>489</v>
       </c>
       <c r="B246" t="s" s="2">
         <v>179</v>
@@ -27450,7 +27465,7 @@
     </row>
     <row r="247">
       <c r="A247" t="s" s="2">
-        <v>486</v>
+        <v>490</v>
       </c>
       <c r="B247" t="s" s="2">
         <v>184</v>
@@ -27476,16 +27491,16 @@
         <v>20</v>
       </c>
       <c r="K247" t="s" s="2">
-        <v>487</v>
+        <v>491</v>
       </c>
       <c r="L247" t="s" s="2">
-        <v>488</v>
+        <v>492</v>
       </c>
       <c r="M247" t="s" s="2">
-        <v>489</v>
+        <v>493</v>
       </c>
       <c r="N247" t="s" s="2">
-        <v>490</v>
+        <v>494</v>
       </c>
       <c r="O247" s="2"/>
       <c r="P247" t="s" s="2">
@@ -27552,7 +27567,7 @@
     </row>
     <row r="248">
       <c r="A248" t="s" s="2">
-        <v>491</v>
+        <v>495</v>
       </c>
       <c r="B248" t="s" s="2">
         <v>189</v>
@@ -27652,7 +27667,7 @@
     </row>
     <row r="249">
       <c r="A249" t="s" s="2">
-        <v>492</v>
+        <v>496</v>
       </c>
       <c r="B249" t="s" s="2">
         <v>193</v>
@@ -27752,7 +27767,7 @@
     </row>
     <row r="250">
       <c r="A250" t="s" s="2">
-        <v>493</v>
+        <v>497</v>
       </c>
       <c r="B250" t="s" s="2">
         <v>194</v>
@@ -27854,7 +27869,7 @@
     </row>
     <row r="251">
       <c r="A251" t="s" s="2">
-        <v>494</v>
+        <v>498</v>
       </c>
       <c r="B251" t="s" s="2">
         <v>195</v>
@@ -27958,7 +27973,7 @@
     </row>
     <row r="252">
       <c r="A252" t="s" s="2">
-        <v>495</v>
+        <v>499</v>
       </c>
       <c r="B252" t="s" s="2">
         <v>196</v>
@@ -28060,7 +28075,7 @@
     </row>
     <row r="253">
       <c r="A253" t="s" s="2">
-        <v>496</v>
+        <v>500</v>
       </c>
       <c r="B253" t="s" s="2">
         <v>202</v>
@@ -28162,7 +28177,7 @@
     </row>
     <row r="254">
       <c r="A254" t="s" s="2">
-        <v>497</v>
+        <v>501</v>
       </c>
       <c r="B254" t="s" s="2">
         <v>207</v>
@@ -28262,7 +28277,7 @@
     </row>
     <row r="255">
       <c r="A255" t="s" s="2">
-        <v>498</v>
+        <v>502</v>
       </c>
       <c r="B255" t="s" s="2">
         <v>211</v>
@@ -28362,7 +28377,7 @@
     </row>
     <row r="256">
       <c r="A256" t="s" s="2">
-        <v>499</v>
+        <v>503</v>
       </c>
       <c r="B256" t="s" s="2">
         <v>212</v>
@@ -28464,7 +28479,7 @@
     </row>
     <row r="257">
       <c r="A257" t="s" s="2">
-        <v>500</v>
+        <v>504</v>
       </c>
       <c r="B257" t="s" s="2">
         <v>213</v>
@@ -28568,7 +28583,7 @@
     </row>
     <row r="258">
       <c r="A258" t="s" s="2">
-        <v>501</v>
+        <v>505</v>
       </c>
       <c r="B258" t="s" s="2">
         <v>214</v>
@@ -28666,7 +28681,7 @@
     </row>
     <row r="259">
       <c r="A259" t="s" s="2">
-        <v>502</v>
+        <v>506</v>
       </c>
       <c r="B259" t="s" s="2">
         <v>220</v>
@@ -28768,7 +28783,7 @@
     </row>
     <row r="260">
       <c r="A260" t="s" s="2">
-        <v>503</v>
+        <v>507</v>
       </c>
       <c r="B260" t="s" s="2">
         <v>224</v>
@@ -28868,7 +28883,7 @@
     </row>
     <row r="261">
       <c r="A261" t="s" s="2">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="B261" t="s" s="2">
         <v>227</v>
@@ -28968,7 +28983,7 @@
     </row>
     <row r="262">
       <c r="A262" t="s" s="2">
-        <v>505</v>
+        <v>509</v>
       </c>
       <c r="B262" t="s" s="2">
         <v>230</v>
@@ -29068,7 +29083,7 @@
     </row>
     <row r="263">
       <c r="A263" t="s" s="2">
-        <v>506</v>
+        <v>510</v>
       </c>
       <c r="B263" t="s" s="2">
         <v>233</v>
@@ -29168,7 +29183,7 @@
     </row>
     <row r="264">
       <c r="A264" t="s" s="2">
-        <v>507</v>
+        <v>511</v>
       </c>
       <c r="B264" t="s" s="2">
         <v>236</v>
@@ -29268,7 +29283,7 @@
     </row>
     <row r="265">
       <c r="A265" t="s" s="2">
-        <v>508</v>
+        <v>512</v>
       </c>
       <c r="B265" t="s" s="2">
         <v>240</v>
@@ -29368,7 +29383,7 @@
     </row>
     <row r="266">
       <c r="A266" t="s" s="2">
-        <v>509</v>
+        <v>513</v>
       </c>
       <c r="B266" t="s" s="2">
         <v>241</v>
@@ -29470,7 +29485,7 @@
     </row>
     <row r="267">
       <c r="A267" t="s" s="2">
-        <v>510</v>
+        <v>514</v>
       </c>
       <c r="B267" t="s" s="2">
         <v>242</v>
@@ -29574,7 +29589,7 @@
     </row>
     <row r="268">
       <c r="A268" t="s" s="2">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c r="B268" t="s" s="2">
         <v>243</v>
@@ -29674,7 +29689,7 @@
     </row>
     <row r="269">
       <c r="A269" t="s" s="2">
-        <v>512</v>
+        <v>516</v>
       </c>
       <c r="B269" t="s" s="2">
         <v>246</v>
@@ -29774,7 +29789,7 @@
     </row>
     <row r="270">
       <c r="A270" t="s" s="2">
-        <v>513</v>
+        <v>517</v>
       </c>
       <c r="B270" t="s" s="2">
         <v>249</v>
@@ -29876,7 +29891,7 @@
     </row>
     <row r="271">
       <c r="A271" t="s" s="2">
-        <v>514</v>
+        <v>518</v>
       </c>
       <c r="B271" t="s" s="2">
         <v>253</v>
@@ -29978,7 +29993,7 @@
     </row>
     <row r="272">
       <c r="A272" t="s" s="2">
-        <v>515</v>
+        <v>519</v>
       </c>
       <c r="B272" t="s" s="2">
         <v>257</v>
@@ -30080,13 +30095,13 @@
     </row>
     <row r="273">
       <c r="A273" t="s" s="2">
-        <v>516</v>
+        <v>520</v>
       </c>
       <c r="B273" t="s" s="2">
         <v>167</v>
       </c>
       <c r="C273" t="s" s="2">
-        <v>517</v>
+        <v>521</v>
       </c>
       <c r="D273" t="s" s="2">
         <v>20</v>
@@ -30182,7 +30197,7 @@
     </row>
     <row r="274">
       <c r="A274" t="s" s="2">
-        <v>518</v>
+        <v>522</v>
       </c>
       <c r="B274" t="s" s="2">
         <v>173</v>
@@ -30282,7 +30297,7 @@
     </row>
     <row r="275">
       <c r="A275" t="s" s="2">
-        <v>519</v>
+        <v>523</v>
       </c>
       <c r="B275" t="s" s="2">
         <v>174</v>
@@ -30384,7 +30399,7 @@
     </row>
     <row r="276">
       <c r="A276" t="s" s="2">
-        <v>520</v>
+        <v>524</v>
       </c>
       <c r="B276" t="s" s="2">
         <v>175</v>
@@ -30488,7 +30503,7 @@
     </row>
     <row r="277">
       <c r="A277" t="s" s="2">
-        <v>521</v>
+        <v>525</v>
       </c>
       <c r="B277" t="s" s="2">
         <v>176</v>
@@ -30514,7 +30529,7 @@
         <v>81</v>
       </c>
       <c r="K277" t="s" s="2">
-        <v>75</v>
+        <v>20</v>
       </c>
       <c r="L277" t="s" s="2">
         <v>177</v>
@@ -30588,7 +30603,7 @@
     </row>
     <row r="278">
       <c r="A278" t="s" s="2">
-        <v>522</v>
+        <v>526</v>
       </c>
       <c r="B278" t="s" s="2">
         <v>179</v>
@@ -30690,7 +30705,7 @@
     </row>
     <row r="279">
       <c r="A279" t="s" s="2">
-        <v>523</v>
+        <v>527</v>
       </c>
       <c r="B279" t="s" s="2">
         <v>184</v>
@@ -30716,13 +30731,13 @@
         <v>20</v>
       </c>
       <c r="K279" t="s" s="2">
-        <v>524</v>
+        <v>528</v>
       </c>
       <c r="L279" t="s" s="2">
-        <v>525</v>
+        <v>529</v>
       </c>
       <c r="M279" t="s" s="2">
-        <v>526</v>
+        <v>530</v>
       </c>
       <c r="N279" s="2"/>
       <c r="O279" s="2"/>
@@ -30790,7 +30805,7 @@
     </row>
     <row r="280">
       <c r="A280" t="s" s="2">
-        <v>527</v>
+        <v>531</v>
       </c>
       <c r="B280" t="s" s="2">
         <v>189</v>
@@ -30890,7 +30905,7 @@
     </row>
     <row r="281">
       <c r="A281" t="s" s="2">
-        <v>528</v>
+        <v>532</v>
       </c>
       <c r="B281" t="s" s="2">
         <v>193</v>
@@ -30990,7 +31005,7 @@
     </row>
     <row r="282">
       <c r="A282" t="s" s="2">
-        <v>529</v>
+        <v>533</v>
       </c>
       <c r="B282" t="s" s="2">
         <v>194</v>
@@ -31092,7 +31107,7 @@
     </row>
     <row r="283">
       <c r="A283" t="s" s="2">
-        <v>530</v>
+        <v>534</v>
       </c>
       <c r="B283" t="s" s="2">
         <v>195</v>
@@ -31196,7 +31211,7 @@
     </row>
     <row r="284">
       <c r="A284" t="s" s="2">
-        <v>531</v>
+        <v>535</v>
       </c>
       <c r="B284" t="s" s="2">
         <v>196</v>
@@ -31298,7 +31313,7 @@
     </row>
     <row r="285">
       <c r="A285" t="s" s="2">
-        <v>532</v>
+        <v>536</v>
       </c>
       <c r="B285" t="s" s="2">
         <v>202</v>
@@ -31400,7 +31415,7 @@
     </row>
     <row r="286">
       <c r="A286" t="s" s="2">
-        <v>533</v>
+        <v>537</v>
       </c>
       <c r="B286" t="s" s="2">
         <v>207</v>
@@ -31500,7 +31515,7 @@
     </row>
     <row r="287">
       <c r="A287" t="s" s="2">
-        <v>534</v>
+        <v>538</v>
       </c>
       <c r="B287" t="s" s="2">
         <v>211</v>
@@ -31600,7 +31615,7 @@
     </row>
     <row r="288">
       <c r="A288" t="s" s="2">
-        <v>535</v>
+        <v>539</v>
       </c>
       <c r="B288" t="s" s="2">
         <v>212</v>
@@ -31702,7 +31717,7 @@
     </row>
     <row r="289">
       <c r="A289" t="s" s="2">
-        <v>536</v>
+        <v>540</v>
       </c>
       <c r="B289" t="s" s="2">
         <v>213</v>
@@ -31806,7 +31821,7 @@
     </row>
     <row r="290">
       <c r="A290" t="s" s="2">
-        <v>537</v>
+        <v>541</v>
       </c>
       <c r="B290" t="s" s="2">
         <v>214</v>
@@ -31904,7 +31919,7 @@
     </row>
     <row r="291">
       <c r="A291" t="s" s="2">
-        <v>538</v>
+        <v>542</v>
       </c>
       <c r="B291" t="s" s="2">
         <v>220</v>
@@ -32006,7 +32021,7 @@
     </row>
     <row r="292">
       <c r="A292" t="s" s="2">
-        <v>539</v>
+        <v>543</v>
       </c>
       <c r="B292" t="s" s="2">
         <v>224</v>
@@ -32106,7 +32121,7 @@
     </row>
     <row r="293">
       <c r="A293" t="s" s="2">
-        <v>540</v>
+        <v>544</v>
       </c>
       <c r="B293" t="s" s="2">
         <v>227</v>
@@ -32206,7 +32221,7 @@
     </row>
     <row r="294">
       <c r="A294" t="s" s="2">
-        <v>541</v>
+        <v>545</v>
       </c>
       <c r="B294" t="s" s="2">
         <v>230</v>
@@ -32306,7 +32321,7 @@
     </row>
     <row r="295">
       <c r="A295" t="s" s="2">
-        <v>542</v>
+        <v>546</v>
       </c>
       <c r="B295" t="s" s="2">
         <v>233</v>
@@ -32406,7 +32421,7 @@
     </row>
     <row r="296">
       <c r="A296" t="s" s="2">
-        <v>543</v>
+        <v>547</v>
       </c>
       <c r="B296" t="s" s="2">
         <v>236</v>
@@ -32506,7 +32521,7 @@
     </row>
     <row r="297">
       <c r="A297" t="s" s="2">
-        <v>544</v>
+        <v>548</v>
       </c>
       <c r="B297" t="s" s="2">
         <v>240</v>
@@ -32606,7 +32621,7 @@
     </row>
     <row r="298">
       <c r="A298" t="s" s="2">
-        <v>545</v>
+        <v>549</v>
       </c>
       <c r="B298" t="s" s="2">
         <v>241</v>
@@ -32708,7 +32723,7 @@
     </row>
     <row r="299">
       <c r="A299" t="s" s="2">
-        <v>546</v>
+        <v>550</v>
       </c>
       <c r="B299" t="s" s="2">
         <v>242</v>
@@ -32812,7 +32827,7 @@
     </row>
     <row r="300">
       <c r="A300" t="s" s="2">
-        <v>547</v>
+        <v>551</v>
       </c>
       <c r="B300" t="s" s="2">
         <v>243</v>
@@ -32912,7 +32927,7 @@
     </row>
     <row r="301">
       <c r="A301" t="s" s="2">
-        <v>548</v>
+        <v>552</v>
       </c>
       <c r="B301" t="s" s="2">
         <v>246</v>
@@ -33012,7 +33027,7 @@
     </row>
     <row r="302">
       <c r="A302" t="s" s="2">
-        <v>549</v>
+        <v>553</v>
       </c>
       <c r="B302" t="s" s="2">
         <v>249</v>
@@ -33114,7 +33129,7 @@
     </row>
     <row r="303">
       <c r="A303" t="s" s="2">
-        <v>550</v>
+        <v>554</v>
       </c>
       <c r="B303" t="s" s="2">
         <v>253</v>
@@ -33216,7 +33231,7 @@
     </row>
     <row r="304">
       <c r="A304" t="s" s="2">
-        <v>551</v>
+        <v>555</v>
       </c>
       <c r="B304" t="s" s="2">
         <v>257</v>
@@ -33318,13 +33333,13 @@
     </row>
     <row r="305">
       <c r="A305" t="s" s="2">
-        <v>552</v>
+        <v>556</v>
       </c>
       <c r="B305" t="s" s="2">
         <v>167</v>
       </c>
       <c r="C305" t="s" s="2">
-        <v>553</v>
+        <v>557</v>
       </c>
       <c r="D305" t="s" s="2">
         <v>20</v>
@@ -33420,7 +33435,7 @@
     </row>
     <row r="306">
       <c r="A306" t="s" s="2">
-        <v>554</v>
+        <v>558</v>
       </c>
       <c r="B306" t="s" s="2">
         <v>173</v>
@@ -33520,7 +33535,7 @@
     </row>
     <row r="307">
       <c r="A307" t="s" s="2">
-        <v>555</v>
+        <v>559</v>
       </c>
       <c r="B307" t="s" s="2">
         <v>174</v>
@@ -33622,7 +33637,7 @@
     </row>
     <row r="308">
       <c r="A308" t="s" s="2">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="B308" t="s" s="2">
         <v>175</v>
@@ -33726,7 +33741,7 @@
     </row>
     <row r="309">
       <c r="A309" t="s" s="2">
-        <v>557</v>
+        <v>561</v>
       </c>
       <c r="B309" t="s" s="2">
         <v>176</v>
@@ -33752,7 +33767,7 @@
         <v>81</v>
       </c>
       <c r="K309" t="s" s="2">
-        <v>75</v>
+        <v>20</v>
       </c>
       <c r="L309" t="s" s="2">
         <v>177</v>
@@ -33826,7 +33841,7 @@
     </row>
     <row r="310">
       <c r="A310" t="s" s="2">
-        <v>558</v>
+        <v>562</v>
       </c>
       <c r="B310" t="s" s="2">
         <v>179</v>
@@ -33928,7 +33943,7 @@
     </row>
     <row r="311">
       <c r="A311" t="s" s="2">
-        <v>559</v>
+        <v>563</v>
       </c>
       <c r="B311" t="s" s="2">
         <v>184</v>
@@ -33954,13 +33969,13 @@
         <v>20</v>
       </c>
       <c r="K311" t="s" s="2">
-        <v>560</v>
+        <v>564</v>
       </c>
       <c r="L311" t="s" s="2">
-        <v>561</v>
+        <v>565</v>
       </c>
       <c r="M311" t="s" s="2">
-        <v>562</v>
+        <v>566</v>
       </c>
       <c r="N311" s="2"/>
       <c r="O311" s="2"/>
@@ -34028,7 +34043,7 @@
     </row>
     <row r="312">
       <c r="A312" t="s" s="2">
-        <v>563</v>
+        <v>567</v>
       </c>
       <c r="B312" t="s" s="2">
         <v>189</v>
@@ -34128,7 +34143,7 @@
     </row>
     <row r="313">
       <c r="A313" t="s" s="2">
-        <v>564</v>
+        <v>568</v>
       </c>
       <c r="B313" t="s" s="2">
         <v>193</v>
@@ -34228,7 +34243,7 @@
     </row>
     <row r="314">
       <c r="A314" t="s" s="2">
-        <v>565</v>
+        <v>569</v>
       </c>
       <c r="B314" t="s" s="2">
         <v>194</v>
@@ -34330,7 +34345,7 @@
     </row>
     <row r="315">
       <c r="A315" t="s" s="2">
-        <v>566</v>
+        <v>570</v>
       </c>
       <c r="B315" t="s" s="2">
         <v>195</v>
@@ -34434,7 +34449,7 @@
     </row>
     <row r="316">
       <c r="A316" t="s" s="2">
-        <v>567</v>
+        <v>571</v>
       </c>
       <c r="B316" t="s" s="2">
         <v>196</v>
@@ -34536,7 +34551,7 @@
     </row>
     <row r="317">
       <c r="A317" t="s" s="2">
-        <v>568</v>
+        <v>572</v>
       </c>
       <c r="B317" t="s" s="2">
         <v>202</v>
@@ -34638,7 +34653,7 @@
     </row>
     <row r="318">
       <c r="A318" t="s" s="2">
-        <v>569</v>
+        <v>573</v>
       </c>
       <c r="B318" t="s" s="2">
         <v>207</v>
@@ -34738,7 +34753,7 @@
     </row>
     <row r="319">
       <c r="A319" t="s" s="2">
-        <v>570</v>
+        <v>574</v>
       </c>
       <c r="B319" t="s" s="2">
         <v>211</v>
@@ -34838,7 +34853,7 @@
     </row>
     <row r="320">
       <c r="A320" t="s" s="2">
-        <v>571</v>
+        <v>575</v>
       </c>
       <c r="B320" t="s" s="2">
         <v>212</v>
@@ -34940,7 +34955,7 @@
     </row>
     <row r="321">
       <c r="A321" t="s" s="2">
-        <v>572</v>
+        <v>576</v>
       </c>
       <c r="B321" t="s" s="2">
         <v>213</v>
@@ -35044,7 +35059,7 @@
     </row>
     <row r="322">
       <c r="A322" t="s" s="2">
-        <v>573</v>
+        <v>577</v>
       </c>
       <c r="B322" t="s" s="2">
         <v>214</v>
@@ -35142,7 +35157,7 @@
     </row>
     <row r="323">
       <c r="A323" t="s" s="2">
-        <v>574</v>
+        <v>578</v>
       </c>
       <c r="B323" t="s" s="2">
         <v>220</v>
@@ -35244,7 +35259,7 @@
     </row>
     <row r="324">
       <c r="A324" t="s" s="2">
-        <v>575</v>
+        <v>579</v>
       </c>
       <c r="B324" t="s" s="2">
         <v>224</v>
@@ -35344,7 +35359,7 @@
     </row>
     <row r="325">
       <c r="A325" t="s" s="2">
-        <v>576</v>
+        <v>580</v>
       </c>
       <c r="B325" t="s" s="2">
         <v>227</v>
@@ -35444,7 +35459,7 @@
     </row>
     <row r="326">
       <c r="A326" t="s" s="2">
-        <v>577</v>
+        <v>581</v>
       </c>
       <c r="B326" t="s" s="2">
         <v>230</v>
@@ -35544,7 +35559,7 @@
     </row>
     <row r="327">
       <c r="A327" t="s" s="2">
-        <v>578</v>
+        <v>582</v>
       </c>
       <c r="B327" t="s" s="2">
         <v>233</v>
@@ -35644,7 +35659,7 @@
     </row>
     <row r="328">
       <c r="A328" t="s" s="2">
-        <v>579</v>
+        <v>583</v>
       </c>
       <c r="B328" t="s" s="2">
         <v>236</v>
@@ -35744,7 +35759,7 @@
     </row>
     <row r="329">
       <c r="A329" t="s" s="2">
-        <v>580</v>
+        <v>584</v>
       </c>
       <c r="B329" t="s" s="2">
         <v>240</v>
@@ -35844,7 +35859,7 @@
     </row>
     <row r="330">
       <c r="A330" t="s" s="2">
-        <v>581</v>
+        <v>585</v>
       </c>
       <c r="B330" t="s" s="2">
         <v>241</v>
@@ -35946,7 +35961,7 @@
     </row>
     <row r="331">
       <c r="A331" t="s" s="2">
-        <v>582</v>
+        <v>586</v>
       </c>
       <c r="B331" t="s" s="2">
         <v>242</v>
@@ -36050,7 +36065,7 @@
     </row>
     <row r="332">
       <c r="A332" t="s" s="2">
-        <v>583</v>
+        <v>587</v>
       </c>
       <c r="B332" t="s" s="2">
         <v>243</v>
@@ -36150,7 +36165,7 @@
     </row>
     <row r="333">
       <c r="A333" t="s" s="2">
-        <v>584</v>
+        <v>588</v>
       </c>
       <c r="B333" t="s" s="2">
         <v>246</v>
@@ -36250,7 +36265,7 @@
     </row>
     <row r="334">
       <c r="A334" t="s" s="2">
-        <v>585</v>
+        <v>589</v>
       </c>
       <c r="B334" t="s" s="2">
         <v>249</v>
@@ -36352,7 +36367,7 @@
     </row>
     <row r="335">
       <c r="A335" t="s" s="2">
-        <v>586</v>
+        <v>590</v>
       </c>
       <c r="B335" t="s" s="2">
         <v>253</v>
@@ -36454,7 +36469,7 @@
     </row>
     <row r="336">
       <c r="A336" t="s" s="2">
-        <v>587</v>
+        <v>591</v>
       </c>
       <c r="B336" t="s" s="2">
         <v>257</v>
@@ -36556,13 +36571,13 @@
     </row>
     <row r="337">
       <c r="A337" t="s" s="2">
-        <v>588</v>
+        <v>592</v>
       </c>
       <c r="B337" t="s" s="2">
         <v>167</v>
       </c>
       <c r="C337" t="s" s="2">
-        <v>589</v>
+        <v>593</v>
       </c>
       <c r="D337" t="s" s="2">
         <v>20</v>
@@ -36658,7 +36673,7 @@
     </row>
     <row r="338">
       <c r="A338" t="s" s="2">
-        <v>590</v>
+        <v>594</v>
       </c>
       <c r="B338" t="s" s="2">
         <v>173</v>
@@ -36758,7 +36773,7 @@
     </row>
     <row r="339">
       <c r="A339" t="s" s="2">
-        <v>591</v>
+        <v>595</v>
       </c>
       <c r="B339" t="s" s="2">
         <v>174</v>
@@ -36860,7 +36875,7 @@
     </row>
     <row r="340">
       <c r="A340" t="s" s="2">
-        <v>592</v>
+        <v>596</v>
       </c>
       <c r="B340" t="s" s="2">
         <v>175</v>
@@ -36964,7 +36979,7 @@
     </row>
     <row r="341">
       <c r="A341" t="s" s="2">
-        <v>593</v>
+        <v>597</v>
       </c>
       <c r="B341" t="s" s="2">
         <v>176</v>
@@ -36990,7 +37005,7 @@
         <v>81</v>
       </c>
       <c r="K341" t="s" s="2">
-        <v>75</v>
+        <v>20</v>
       </c>
       <c r="L341" t="s" s="2">
         <v>177</v>
@@ -37064,7 +37079,7 @@
     </row>
     <row r="342">
       <c r="A342" t="s" s="2">
-        <v>594</v>
+        <v>598</v>
       </c>
       <c r="B342" t="s" s="2">
         <v>179</v>
@@ -37166,14 +37181,14 @@
     </row>
     <row r="343">
       <c r="A343" t="s" s="2">
-        <v>595</v>
+        <v>599</v>
       </c>
       <c r="B343" t="s" s="2">
         <v>184</v>
       </c>
       <c r="C343" s="2"/>
       <c r="D343" t="s" s="2">
-        <v>596</v>
+        <v>600</v>
       </c>
       <c r="E343" s="2"/>
       <c r="F343" t="s" s="2">
@@ -37192,16 +37207,16 @@
         <v>20</v>
       </c>
       <c r="K343" t="s" s="2">
-        <v>597</v>
+        <v>601</v>
       </c>
       <c r="L343" t="s" s="2">
-        <v>598</v>
+        <v>602</v>
       </c>
       <c r="M343" t="s" s="2">
-        <v>599</v>
+        <v>603</v>
       </c>
       <c r="N343" t="s" s="2">
-        <v>600</v>
+        <v>604</v>
       </c>
       <c r="O343" s="2"/>
       <c r="P343" t="s" s="2">
@@ -37268,7 +37283,7 @@
     </row>
     <row r="344">
       <c r="A344" t="s" s="2">
-        <v>601</v>
+        <v>605</v>
       </c>
       <c r="B344" t="s" s="2">
         <v>189</v>
@@ -37368,7 +37383,7 @@
     </row>
     <row r="345">
       <c r="A345" t="s" s="2">
-        <v>602</v>
+        <v>606</v>
       </c>
       <c r="B345" t="s" s="2">
         <v>193</v>
@@ -37468,7 +37483,7 @@
     </row>
     <row r="346">
       <c r="A346" t="s" s="2">
-        <v>603</v>
+        <v>607</v>
       </c>
       <c r="B346" t="s" s="2">
         <v>194</v>
@@ -37570,7 +37585,7 @@
     </row>
     <row r="347">
       <c r="A347" t="s" s="2">
-        <v>604</v>
+        <v>608</v>
       </c>
       <c r="B347" t="s" s="2">
         <v>195</v>
@@ -37674,7 +37689,7 @@
     </row>
     <row r="348">
       <c r="A348" t="s" s="2">
-        <v>605</v>
+        <v>609</v>
       </c>
       <c r="B348" t="s" s="2">
         <v>196</v>
@@ -37776,7 +37791,7 @@
     </row>
     <row r="349">
       <c r="A349" t="s" s="2">
-        <v>606</v>
+        <v>610</v>
       </c>
       <c r="B349" t="s" s="2">
         <v>202</v>
@@ -37878,7 +37893,7 @@
     </row>
     <row r="350">
       <c r="A350" t="s" s="2">
-        <v>607</v>
+        <v>611</v>
       </c>
       <c r="B350" t="s" s="2">
         <v>207</v>
@@ -37978,7 +37993,7 @@
     </row>
     <row r="351">
       <c r="A351" t="s" s="2">
-        <v>608</v>
+        <v>612</v>
       </c>
       <c r="B351" t="s" s="2">
         <v>211</v>
@@ -38078,7 +38093,7 @@
     </row>
     <row r="352">
       <c r="A352" t="s" s="2">
-        <v>609</v>
+        <v>613</v>
       </c>
       <c r="B352" t="s" s="2">
         <v>212</v>
@@ -38180,7 +38195,7 @@
     </row>
     <row r="353">
       <c r="A353" t="s" s="2">
-        <v>610</v>
+        <v>614</v>
       </c>
       <c r="B353" t="s" s="2">
         <v>213</v>
@@ -38284,7 +38299,7 @@
     </row>
     <row r="354">
       <c r="A354" t="s" s="2">
-        <v>611</v>
+        <v>615</v>
       </c>
       <c r="B354" t="s" s="2">
         <v>214</v>
@@ -38382,7 +38397,7 @@
     </row>
     <row r="355">
       <c r="A355" t="s" s="2">
-        <v>612</v>
+        <v>616</v>
       </c>
       <c r="B355" t="s" s="2">
         <v>220</v>
@@ -38484,7 +38499,7 @@
     </row>
     <row r="356">
       <c r="A356" t="s" s="2">
-        <v>613</v>
+        <v>617</v>
       </c>
       <c r="B356" t="s" s="2">
         <v>224</v>
@@ -38584,7 +38599,7 @@
     </row>
     <row r="357">
       <c r="A357" t="s" s="2">
-        <v>614</v>
+        <v>618</v>
       </c>
       <c r="B357" t="s" s="2">
         <v>227</v>
@@ -38684,7 +38699,7 @@
     </row>
     <row r="358">
       <c r="A358" t="s" s="2">
-        <v>615</v>
+        <v>619</v>
       </c>
       <c r="B358" t="s" s="2">
         <v>230</v>
@@ -38784,7 +38799,7 @@
     </row>
     <row r="359">
       <c r="A359" t="s" s="2">
-        <v>616</v>
+        <v>620</v>
       </c>
       <c r="B359" t="s" s="2">
         <v>233</v>
@@ -38884,7 +38899,7 @@
     </row>
     <row r="360">
       <c r="A360" t="s" s="2">
-        <v>617</v>
+        <v>621</v>
       </c>
       <c r="B360" t="s" s="2">
         <v>236</v>
@@ -38984,7 +38999,7 @@
     </row>
     <row r="361">
       <c r="A361" t="s" s="2">
-        <v>618</v>
+        <v>622</v>
       </c>
       <c r="B361" t="s" s="2">
         <v>240</v>
@@ -39084,7 +39099,7 @@
     </row>
     <row r="362">
       <c r="A362" t="s" s="2">
-        <v>619</v>
+        <v>623</v>
       </c>
       <c r="B362" t="s" s="2">
         <v>241</v>
@@ -39186,7 +39201,7 @@
     </row>
     <row r="363">
       <c r="A363" t="s" s="2">
-        <v>620</v>
+        <v>624</v>
       </c>
       <c r="B363" t="s" s="2">
         <v>242</v>
@@ -39290,7 +39305,7 @@
     </row>
     <row r="364">
       <c r="A364" t="s" s="2">
-        <v>621</v>
+        <v>625</v>
       </c>
       <c r="B364" t="s" s="2">
         <v>243</v>
@@ -39390,7 +39405,7 @@
     </row>
     <row r="365">
       <c r="A365" t="s" s="2">
-        <v>622</v>
+        <v>626</v>
       </c>
       <c r="B365" t="s" s="2">
         <v>246</v>
@@ -39490,7 +39505,7 @@
     </row>
     <row r="366">
       <c r="A366" t="s" s="2">
-        <v>623</v>
+        <v>627</v>
       </c>
       <c r="B366" t="s" s="2">
         <v>249</v>
@@ -39592,7 +39607,7 @@
     </row>
     <row r="367">
       <c r="A367" t="s" s="2">
-        <v>624</v>
+        <v>628</v>
       </c>
       <c r="B367" t="s" s="2">
         <v>253</v>
@@ -39694,7 +39709,7 @@
     </row>
     <row r="368">
       <c r="A368" t="s" s="2">
-        <v>625</v>
+        <v>629</v>
       </c>
       <c r="B368" t="s" s="2">
         <v>257</v>
@@ -39796,13 +39811,13 @@
     </row>
     <row r="369">
       <c r="A369" t="s" s="2">
-        <v>626</v>
+        <v>630</v>
       </c>
       <c r="B369" t="s" s="2">
         <v>167</v>
       </c>
       <c r="C369" t="s" s="2">
-        <v>627</v>
+        <v>631</v>
       </c>
       <c r="D369" t="s" s="2">
         <v>20</v>
@@ -39898,7 +39913,7 @@
     </row>
     <row r="370">
       <c r="A370" t="s" s="2">
-        <v>628</v>
+        <v>632</v>
       </c>
       <c r="B370" t="s" s="2">
         <v>173</v>
@@ -39998,7 +40013,7 @@
     </row>
     <row r="371">
       <c r="A371" t="s" s="2">
-        <v>629</v>
+        <v>633</v>
       </c>
       <c r="B371" t="s" s="2">
         <v>174</v>
@@ -40100,7 +40115,7 @@
     </row>
     <row r="372">
       <c r="A372" t="s" s="2">
-        <v>630</v>
+        <v>634</v>
       </c>
       <c r="B372" t="s" s="2">
         <v>175</v>
@@ -40204,7 +40219,7 @@
     </row>
     <row r="373">
       <c r="A373" t="s" s="2">
-        <v>631</v>
+        <v>635</v>
       </c>
       <c r="B373" t="s" s="2">
         <v>176</v>
@@ -40304,7 +40319,7 @@
     </row>
     <row r="374">
       <c r="A374" t="s" s="2">
-        <v>632</v>
+        <v>636</v>
       </c>
       <c r="B374" t="s" s="2">
         <v>179</v>
@@ -40406,7 +40421,7 @@
     </row>
     <row r="375">
       <c r="A375" t="s" s="2">
-        <v>633</v>
+        <v>637</v>
       </c>
       <c r="B375" t="s" s="2">
         <v>184</v>
@@ -40432,7 +40447,7 @@
         <v>81</v>
       </c>
       <c r="K375" t="s" s="2">
-        <v>634</v>
+        <v>638</v>
       </c>
       <c r="L375" t="s" s="2">
         <v>186</v>
@@ -40506,7 +40521,7 @@
     </row>
     <row r="376">
       <c r="A376" t="s" s="2">
-        <v>635</v>
+        <v>639</v>
       </c>
       <c r="B376" t="s" s="2">
         <v>189</v>
@@ -40606,7 +40621,7 @@
     </row>
     <row r="377">
       <c r="A377" t="s" s="2">
-        <v>636</v>
+        <v>640</v>
       </c>
       <c r="B377" t="s" s="2">
         <v>193</v>
@@ -40706,7 +40721,7 @@
     </row>
     <row r="378">
       <c r="A378" t="s" s="2">
-        <v>637</v>
+        <v>641</v>
       </c>
       <c r="B378" t="s" s="2">
         <v>194</v>
@@ -40808,7 +40823,7 @@
     </row>
     <row r="379">
       <c r="A379" t="s" s="2">
-        <v>638</v>
+        <v>642</v>
       </c>
       <c r="B379" t="s" s="2">
         <v>195</v>
@@ -40912,7 +40927,7 @@
     </row>
     <row r="380">
       <c r="A380" t="s" s="2">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="B380" t="s" s="2">
         <v>196</v>
@@ -41014,7 +41029,7 @@
     </row>
     <row r="381">
       <c r="A381" t="s" s="2">
-        <v>640</v>
+        <v>644</v>
       </c>
       <c r="B381" t="s" s="2">
         <v>202</v>
@@ -41116,7 +41131,7 @@
     </row>
     <row r="382">
       <c r="A382" t="s" s="2">
-        <v>641</v>
+        <v>645</v>
       </c>
       <c r="B382" t="s" s="2">
         <v>207</v>
@@ -41216,7 +41231,7 @@
     </row>
     <row r="383">
       <c r="A383" t="s" s="2">
-        <v>642</v>
+        <v>646</v>
       </c>
       <c r="B383" t="s" s="2">
         <v>211</v>
@@ -41316,7 +41331,7 @@
     </row>
     <row r="384">
       <c r="A384" t="s" s="2">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="B384" t="s" s="2">
         <v>212</v>
@@ -41418,7 +41433,7 @@
     </row>
     <row r="385">
       <c r="A385" t="s" s="2">
-        <v>644</v>
+        <v>648</v>
       </c>
       <c r="B385" t="s" s="2">
         <v>213</v>
@@ -41522,7 +41537,7 @@
     </row>
     <row r="386">
       <c r="A386" t="s" s="2">
-        <v>645</v>
+        <v>649</v>
       </c>
       <c r="B386" t="s" s="2">
         <v>214</v>
@@ -41551,7 +41566,7 @@
         <v>100</v>
       </c>
       <c r="L386" t="s" s="2">
-        <v>646</v>
+        <v>650</v>
       </c>
       <c r="M386" t="s" s="2">
         <v>216</v>
@@ -41585,7 +41600,7 @@
       </c>
       <c r="Y386" s="2"/>
       <c r="Z386" t="s" s="2">
-        <v>647</v>
+        <v>651</v>
       </c>
       <c r="AA386" t="s" s="2">
         <v>20</v>
@@ -41620,7 +41635,7 @@
     </row>
     <row r="387">
       <c r="A387" t="s" s="2">
-        <v>648</v>
+        <v>652</v>
       </c>
       <c r="B387" t="s" s="2">
         <v>220</v>
@@ -41722,7 +41737,7 @@
     </row>
     <row r="388">
       <c r="A388" t="s" s="2">
-        <v>649</v>
+        <v>653</v>
       </c>
       <c r="B388" t="s" s="2">
         <v>224</v>
@@ -41822,7 +41837,7 @@
     </row>
     <row r="389">
       <c r="A389" t="s" s="2">
-        <v>650</v>
+        <v>654</v>
       </c>
       <c r="B389" t="s" s="2">
         <v>227</v>
@@ -41922,7 +41937,7 @@
     </row>
     <row r="390">
       <c r="A390" t="s" s="2">
-        <v>651</v>
+        <v>655</v>
       </c>
       <c r="B390" t="s" s="2">
         <v>230</v>
@@ -42022,7 +42037,7 @@
     </row>
     <row r="391">
       <c r="A391" t="s" s="2">
-        <v>652</v>
+        <v>656</v>
       </c>
       <c r="B391" t="s" s="2">
         <v>233</v>
@@ -42122,7 +42137,7 @@
     </row>
     <row r="392">
       <c r="A392" t="s" s="2">
-        <v>653</v>
+        <v>657</v>
       </c>
       <c r="B392" t="s" s="2">
         <v>236</v>
@@ -42222,7 +42237,7 @@
     </row>
     <row r="393">
       <c r="A393" t="s" s="2">
-        <v>654</v>
+        <v>658</v>
       </c>
       <c r="B393" t="s" s="2">
         <v>240</v>
@@ -42322,7 +42337,7 @@
     </row>
     <row r="394">
       <c r="A394" t="s" s="2">
-        <v>655</v>
+        <v>659</v>
       </c>
       <c r="B394" t="s" s="2">
         <v>241</v>
@@ -42424,7 +42439,7 @@
     </row>
     <row r="395">
       <c r="A395" t="s" s="2">
-        <v>656</v>
+        <v>660</v>
       </c>
       <c r="B395" t="s" s="2">
         <v>242</v>
@@ -42528,7 +42543,7 @@
     </row>
     <row r="396">
       <c r="A396" t="s" s="2">
-        <v>657</v>
+        <v>661</v>
       </c>
       <c r="B396" t="s" s="2">
         <v>243</v>
@@ -42628,7 +42643,7 @@
     </row>
     <row r="397">
       <c r="A397" t="s" s="2">
-        <v>658</v>
+        <v>662</v>
       </c>
       <c r="B397" t="s" s="2">
         <v>246</v>
@@ -42728,7 +42743,7 @@
     </row>
     <row r="398">
       <c r="A398" t="s" s="2">
-        <v>659</v>
+        <v>663</v>
       </c>
       <c r="B398" t="s" s="2">
         <v>249</v>
@@ -42830,7 +42845,7 @@
     </row>
     <row r="399">
       <c r="A399" t="s" s="2">
-        <v>660</v>
+        <v>664</v>
       </c>
       <c r="B399" t="s" s="2">
         <v>253</v>
@@ -42932,7 +42947,7 @@
     </row>
     <row r="400">
       <c r="A400" t="s" s="2">
-        <v>661</v>
+        <v>665</v>
       </c>
       <c r="B400" t="s" s="2">
         <v>257</v>
@@ -43034,13 +43049,13 @@
     </row>
     <row r="401">
       <c r="A401" t="s" s="2">
-        <v>662</v>
+        <v>666</v>
       </c>
       <c r="B401" t="s" s="2">
         <v>167</v>
       </c>
       <c r="C401" t="s" s="2">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="D401" t="s" s="2">
         <v>20</v>
@@ -43136,7 +43151,7 @@
     </row>
     <row r="402">
       <c r="A402" t="s" s="2">
-        <v>664</v>
+        <v>668</v>
       </c>
       <c r="B402" t="s" s="2">
         <v>173</v>
@@ -43236,7 +43251,7 @@
     </row>
     <row r="403">
       <c r="A403" t="s" s="2">
-        <v>665</v>
+        <v>669</v>
       </c>
       <c r="B403" t="s" s="2">
         <v>174</v>
@@ -43338,7 +43353,7 @@
     </row>
     <row r="404">
       <c r="A404" t="s" s="2">
-        <v>666</v>
+        <v>670</v>
       </c>
       <c r="B404" t="s" s="2">
         <v>175</v>
@@ -43442,7 +43457,7 @@
     </row>
     <row r="405">
       <c r="A405" t="s" s="2">
-        <v>667</v>
+        <v>671</v>
       </c>
       <c r="B405" t="s" s="2">
         <v>176</v>
@@ -43542,7 +43557,7 @@
     </row>
     <row r="406">
       <c r="A406" t="s" s="2">
-        <v>668</v>
+        <v>672</v>
       </c>
       <c r="B406" t="s" s="2">
         <v>179</v>
@@ -43644,7 +43659,7 @@
     </row>
     <row r="407">
       <c r="A407" t="s" s="2">
-        <v>669</v>
+        <v>673</v>
       </c>
       <c r="B407" t="s" s="2">
         <v>184</v>
@@ -43670,7 +43685,7 @@
         <v>81</v>
       </c>
       <c r="K407" t="s" s="2">
-        <v>670</v>
+        <v>674</v>
       </c>
       <c r="L407" t="s" s="2">
         <v>186</v>
@@ -43744,7 +43759,7 @@
     </row>
     <row r="408">
       <c r="A408" t="s" s="2">
-        <v>671</v>
+        <v>675</v>
       </c>
       <c r="B408" t="s" s="2">
         <v>189</v>
@@ -43844,7 +43859,7 @@
     </row>
     <row r="409">
       <c r="A409" t="s" s="2">
-        <v>672</v>
+        <v>676</v>
       </c>
       <c r="B409" t="s" s="2">
         <v>193</v>
@@ -43944,7 +43959,7 @@
     </row>
     <row r="410">
       <c r="A410" t="s" s="2">
-        <v>673</v>
+        <v>677</v>
       </c>
       <c r="B410" t="s" s="2">
         <v>194</v>
@@ -44046,7 +44061,7 @@
     </row>
     <row r="411">
       <c r="A411" t="s" s="2">
-        <v>674</v>
+        <v>678</v>
       </c>
       <c r="B411" t="s" s="2">
         <v>195</v>
@@ -44150,7 +44165,7 @@
     </row>
     <row r="412">
       <c r="A412" t="s" s="2">
-        <v>675</v>
+        <v>679</v>
       </c>
       <c r="B412" t="s" s="2">
         <v>196</v>
@@ -44252,7 +44267,7 @@
     </row>
     <row r="413">
       <c r="A413" t="s" s="2">
-        <v>676</v>
+        <v>680</v>
       </c>
       <c r="B413" t="s" s="2">
         <v>202</v>
@@ -44354,7 +44369,7 @@
     </row>
     <row r="414">
       <c r="A414" t="s" s="2">
-        <v>677</v>
+        <v>681</v>
       </c>
       <c r="B414" t="s" s="2">
         <v>207</v>
@@ -44454,7 +44469,7 @@
     </row>
     <row r="415">
       <c r="A415" t="s" s="2">
-        <v>678</v>
+        <v>682</v>
       </c>
       <c r="B415" t="s" s="2">
         <v>211</v>
@@ -44554,7 +44569,7 @@
     </row>
     <row r="416">
       <c r="A416" t="s" s="2">
-        <v>679</v>
+        <v>683</v>
       </c>
       <c r="B416" t="s" s="2">
         <v>212</v>
@@ -44656,7 +44671,7 @@
     </row>
     <row r="417">
       <c r="A417" t="s" s="2">
-        <v>680</v>
+        <v>684</v>
       </c>
       <c r="B417" t="s" s="2">
         <v>213</v>
@@ -44760,7 +44775,7 @@
     </row>
     <row r="418">
       <c r="A418" t="s" s="2">
-        <v>681</v>
+        <v>685</v>
       </c>
       <c r="B418" t="s" s="2">
         <v>214</v>
@@ -44789,7 +44804,7 @@
         <v>100</v>
       </c>
       <c r="L418" t="s" s="2">
-        <v>646</v>
+        <v>650</v>
       </c>
       <c r="M418" t="s" s="2">
         <v>216</v>
@@ -44823,7 +44838,7 @@
       </c>
       <c r="Y418" s="2"/>
       <c r="Z418" t="s" s="2">
-        <v>647</v>
+        <v>651</v>
       </c>
       <c r="AA418" t="s" s="2">
         <v>20</v>
@@ -44858,7 +44873,7 @@
     </row>
     <row r="419">
       <c r="A419" t="s" s="2">
-        <v>682</v>
+        <v>686</v>
       </c>
       <c r="B419" t="s" s="2">
         <v>220</v>
@@ -44960,7 +44975,7 @@
     </row>
     <row r="420">
       <c r="A420" t="s" s="2">
-        <v>683</v>
+        <v>687</v>
       </c>
       <c r="B420" t="s" s="2">
         <v>224</v>
@@ -45060,7 +45075,7 @@
     </row>
     <row r="421">
       <c r="A421" t="s" s="2">
-        <v>684</v>
+        <v>688</v>
       </c>
       <c r="B421" t="s" s="2">
         <v>227</v>
@@ -45160,7 +45175,7 @@
     </row>
     <row r="422">
       <c r="A422" t="s" s="2">
-        <v>685</v>
+        <v>689</v>
       </c>
       <c r="B422" t="s" s="2">
         <v>230</v>
@@ -45260,7 +45275,7 @@
     </row>
     <row r="423">
       <c r="A423" t="s" s="2">
-        <v>686</v>
+        <v>690</v>
       </c>
       <c r="B423" t="s" s="2">
         <v>233</v>
@@ -45360,7 +45375,7 @@
     </row>
     <row r="424">
       <c r="A424" t="s" s="2">
-        <v>687</v>
+        <v>691</v>
       </c>
       <c r="B424" t="s" s="2">
         <v>236</v>
@@ -45460,7 +45475,7 @@
     </row>
     <row r="425">
       <c r="A425" t="s" s="2">
-        <v>688</v>
+        <v>692</v>
       </c>
       <c r="B425" t="s" s="2">
         <v>240</v>
@@ -45560,7 +45575,7 @@
     </row>
     <row r="426">
       <c r="A426" t="s" s="2">
-        <v>689</v>
+        <v>693</v>
       </c>
       <c r="B426" t="s" s="2">
         <v>241</v>
@@ -45662,7 +45677,7 @@
     </row>
     <row r="427">
       <c r="A427" t="s" s="2">
-        <v>690</v>
+        <v>694</v>
       </c>
       <c r="B427" t="s" s="2">
         <v>242</v>
@@ -45766,7 +45781,7 @@
     </row>
     <row r="428">
       <c r="A428" t="s" s="2">
-        <v>691</v>
+        <v>695</v>
       </c>
       <c r="B428" t="s" s="2">
         <v>243</v>
@@ -45866,7 +45881,7 @@
     </row>
     <row r="429">
       <c r="A429" t="s" s="2">
-        <v>692</v>
+        <v>696</v>
       </c>
       <c r="B429" t="s" s="2">
         <v>246</v>
@@ -45966,7 +45981,7 @@
     </row>
     <row r="430">
       <c r="A430" t="s" s="2">
-        <v>693</v>
+        <v>697</v>
       </c>
       <c r="B430" t="s" s="2">
         <v>249</v>
@@ -46068,7 +46083,7 @@
     </row>
     <row r="431">
       <c r="A431" t="s" s="2">
-        <v>694</v>
+        <v>698</v>
       </c>
       <c r="B431" t="s" s="2">
         <v>253</v>
@@ -46170,7 +46185,7 @@
     </row>
     <row r="432">
       <c r="A432" t="s" s="2">
-        <v>695</v>
+        <v>699</v>
       </c>
       <c r="B432" t="s" s="2">
         <v>257</v>
@@ -46272,10 +46287,10 @@
     </row>
     <row r="433">
       <c r="A433" t="s" s="2">
-        <v>696</v>
+        <v>700</v>
       </c>
       <c r="B433" t="s" s="2">
-        <v>696</v>
+        <v>700</v>
       </c>
       <c r="C433" s="2"/>
       <c r="D433" t="s" s="2">
@@ -46298,19 +46313,19 @@
         <v>81</v>
       </c>
       <c r="K433" t="s" s="2">
-        <v>697</v>
+        <v>701</v>
       </c>
       <c r="L433" t="s" s="2">
-        <v>698</v>
+        <v>702</v>
       </c>
       <c r="M433" t="s" s="2">
-        <v>699</v>
+        <v>703</v>
       </c>
       <c r="N433" t="s" s="2">
-        <v>700</v>
+        <v>704</v>
       </c>
       <c r="O433" t="s" s="2">
-        <v>701</v>
+        <v>705</v>
       </c>
       <c r="P433" t="s" s="2">
         <v>20</v>
@@ -46359,7 +46374,7 @@
         <v>20</v>
       </c>
       <c r="AF433" t="s" s="2">
-        <v>696</v>
+        <v>700</v>
       </c>
       <c r="AG433" t="s" s="2">
         <v>73</v>
@@ -46376,10 +46391,10 @@
     </row>
     <row r="434">
       <c r="A434" t="s" s="2">
-        <v>702</v>
+        <v>706</v>
       </c>
       <c r="B434" t="s" s="2">
-        <v>702</v>
+        <v>706</v>
       </c>
       <c r="C434" s="2"/>
       <c r="D434" t="s" s="2">
@@ -46402,16 +46417,16 @@
         <v>81</v>
       </c>
       <c r="K434" t="s" s="2">
-        <v>703</v>
+        <v>707</v>
       </c>
       <c r="L434" t="s" s="2">
-        <v>704</v>
+        <v>708</v>
       </c>
       <c r="M434" t="s" s="2">
-        <v>705</v>
+        <v>709</v>
       </c>
       <c r="N434" t="s" s="2">
-        <v>706</v>
+        <v>710</v>
       </c>
       <c r="O434" s="2"/>
       <c r="P434" t="s" s="2">
@@ -46461,7 +46476,7 @@
         <v>20</v>
       </c>
       <c r="AF434" t="s" s="2">
-        <v>702</v>
+        <v>706</v>
       </c>
       <c r="AG434" t="s" s="2">
         <v>73</v>
@@ -46470,7 +46485,7 @@
         <v>80</v>
       </c>
       <c r="AI434" t="s" s="2">
-        <v>707</v>
+        <v>711</v>
       </c>
       <c r="AJ434" t="s" s="2">
         <v>20</v>
